--- a/paper simu/plot_res.xlsx
+++ b/paper simu/plot_res.xlsx
@@ -1,40 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Baptiste\Documents\PhD\Projects\RL_CS\paper simu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0BD652-86CE-4E19-8AE7-32433FAC534B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33E2D50-DB10-47D7-A0E5-69585838D61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{BDAA4270-F7A0-4A3B-A88A-45C29C0C7CE4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BDAA4270-F7A0-4A3B-A88A-45C29C0C7CE4}"/>
   </bookViews>
   <sheets>
     <sheet name="plot_res" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Sample Size</t>
   </si>
   <si>
-    <t>annealing</t>
+    <t>Annealing</t>
   </si>
   <si>
-    <t>random</t>
+    <t>Quintuplets sketch</t>
   </si>
   <si>
-    <t>quadruplets</t>
-  </si>
-  <si>
-    <t>quintuplets</t>
+    <t>Random sketch</t>
   </si>
 </sst>
 </file>
@@ -592,80 +602,17 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Estimate</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> d</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>istance to the maximum for each method</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11859885438848446"/>
-          <c:y val="0.12996932065912437"/>
-          <c:w val="0.80365539213258719"/>
-          <c:h val="0.7491216143983116"/>
+          <c:x val="0.12697835998180934"/>
+          <c:y val="7.2877542442408016E-2"/>
+          <c:w val="0.83072156925840124"/>
+          <c:h val="0.76876175932448132"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -680,7 +627,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>annealing</c:v>
+                  <c:v>Annealing</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -697,11 +644,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -709,80 +656,70 @@
           </c:marker>
           <c:trendline>
             <c:spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln w="9525" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:prstDash val="sysDot"/>
+                <a:prstDash val="lgDash"/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="3"/>
+            <c:trendlineType val="power"/>
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>plot_res!$A$2:$A$20</c:f>
+              <c:f>plot_res!$A$5:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>80</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>100</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>110</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>120</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>130</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>150</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>175</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>200</c:v>
+                  <c:v>275</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>225</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>250</c:v>
+                  <c:v>325</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>275</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>325</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>350</c:v>
-                </c:pt>
-                <c:pt idx="18">
                   <c:v>375</c:v>
                 </c:pt>
               </c:numCache>
@@ -790,66 +727,57 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>plot_res!$B$2:$B$20</c:f>
+              <c:f>plot_res!$B$23:$B$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>2.571E-2</c:v>
+                  <c:v>2.4622222222222225</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.435E-2</c:v>
+                  <c:v>2.2811111111111111</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.3040000000000001E-2</c:v>
+                  <c:v>2.1533333333333338</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.2159999999999999E-2</c:v>
+                  <c:v>1.9577777777777781</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.053E-2</c:v>
+                  <c:v>1.8255555555555558</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9380000000000001E-2</c:v>
+                  <c:v>1.6833333333333336</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.762E-2</c:v>
+                  <c:v>1.5088888888888889</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.643E-2</c:v>
+                  <c:v>1.1233333333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.515E-2</c:v>
+                  <c:v>0.94666666666666677</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.358E-2</c:v>
+                  <c:v>0.89444444444444449</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0109999999999999E-2</c:v>
+                  <c:v>0.7811111111111112</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.5199999999999998E-3</c:v>
+                  <c:v>0.78666666666666674</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.0499999999999999E-3</c:v>
+                  <c:v>0.74777777777777787</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.0299999999999998E-3</c:v>
+                  <c:v>0.67333333333333345</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.0800000000000004E-3</c:v>
+                  <c:v>0.68111111111111111</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>6.7299999999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.0600000000000003E-3</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6.13E-3</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5.7099999999999998E-3</c:v>
+                  <c:v>0.63444444444444448</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -870,7 +798,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>random</c:v>
+                  <c:v>Random sketch</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -883,15 +811,16 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
+            <c:symbol val="square"/>
             <c:size val="5"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
+              <a:noFill/>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -899,9 +828,12 @@
           </c:marker>
           <c:trendline>
             <c:spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln w="22225" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:prstDash val="sysDot"/>
               </a:ln>
@@ -914,65 +846,56 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>plot_res!$A$2:$A$20</c:f>
+              <c:f>plot_res!$A$5:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>80</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>100</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>110</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>120</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>130</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>150</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>175</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>200</c:v>
+                  <c:v>275</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>225</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>250</c:v>
+                  <c:v>325</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>275</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>325</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>350</c:v>
-                </c:pt>
-                <c:pt idx="18">
                   <c:v>375</c:v>
                 </c:pt>
               </c:numCache>
@@ -980,66 +903,57 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>plot_res!$C$2:$C$20</c:f>
+              <c:f>plot_res!$C$23:$C$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>3.2680000000000001E-2</c:v>
+                  <c:v>3.1977777777777781</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.1140000000000001E-2</c:v>
+                  <c:v>3.0811111111111114</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9399999999999999E-2</c:v>
+                  <c:v>2.9644444444444447</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.878E-2</c:v>
+                  <c:v>2.8200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.7730000000000001E-2</c:v>
+                  <c:v>2.7800000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.6679999999999999E-2</c:v>
+                  <c:v>2.6955555555555559</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.538E-2</c:v>
+                  <c:v>2.5777777777777779</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.5020000000000001E-2</c:v>
+                  <c:v>2.2777777777777781</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.426E-2</c:v>
+                  <c:v>2.2088888888888887</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.3199999999999998E-2</c:v>
+                  <c:v>2.1188888888888893</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.0500000000000001E-2</c:v>
+                  <c:v>2.0122222222222224</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.9879999999999998E-2</c:v>
+                  <c:v>1.8988888888888891</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.907E-2</c:v>
+                  <c:v>1.8377777777777777</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.8110000000000001E-2</c:v>
+                  <c:v>1.7133333333333334</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.7090000000000001E-2</c:v>
+                  <c:v>1.6233333333333335</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.6539999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1.542E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1.461E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1.436E-2</c:v>
+                  <c:v>1.5955555555555556</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1052,15 +966,15 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
+          <c:idx val="3"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>plot_res!$D$1</c:f>
+              <c:f>plot_res!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>quadruplets</c:v>
+                  <c:v>Quintuplets sketch</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1073,15 +987,16 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
+            <c:symbol val="triangle"/>
             <c:size val="5"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
+              <a:noFill/>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent3"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -1089,11 +1004,14 @@
           </c:marker>
           <c:trendline>
             <c:spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln w="12700" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent3"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:prstDash val="sysDot"/>
+                <a:prstDash val="sysDash"/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -1104,65 +1022,56 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>plot_res!$A$2:$A$20</c:f>
+              <c:f>plot_res!$A$5:$A$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>80</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>100</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>110</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>120</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>130</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>150</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>175</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>200</c:v>
+                  <c:v>275</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>225</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>250</c:v>
+                  <c:v>325</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>275</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>325</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>350</c:v>
-                </c:pt>
-                <c:pt idx="18">
                   <c:v>375</c:v>
                 </c:pt>
               </c:numCache>
@@ -1170,256 +1079,57 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>plot_res!$D$2:$D$20</c:f>
+              <c:f>plot_res!$E$23:$E$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>2.6290000000000001E-2</c:v>
+                  <c:v>2.2466666666666666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3E-2</c:v>
+                  <c:v>1.9788888888888889</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.052E-2</c:v>
+                  <c:v>1.907777777777778</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9480000000000001E-2</c:v>
+                  <c:v>1.6055555555555556</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.7229999999999999E-2</c:v>
+                  <c:v>1.5655555555555556</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.738E-2</c:v>
+                  <c:v>1.3811111111111112</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.6109999999999999E-2</c:v>
+                  <c:v>1.1533333333333335</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.4749999999999999E-2</c:v>
+                  <c:v>0.95777777777777773</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.3860000000000001E-2</c:v>
+                  <c:v>0.79555555555555557</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.3310000000000001E-2</c:v>
+                  <c:v>0.64333333333333342</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.132E-2</c:v>
+                  <c:v>0.50555555555555565</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.92E-3</c:v>
+                  <c:v>0.46444444444444444</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.9700000000000005E-3</c:v>
+                  <c:v>0.37333333333333335</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.7400000000000004E-3</c:v>
+                  <c:v>0.34222222222222221</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.4400000000000004E-3</c:v>
+                  <c:v>0.3066666666666667</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>7.0600000000000003E-3</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.43E-3</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6.2300000000000003E-3</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5.7000000000000002E-3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-5A02-4183-8769-A8BA3362F1E1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>plot_res!$E$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>quintuplets</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="4"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>plot_res!$A$2:$A$20</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>110</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>120</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>130</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>150</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>175</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>200</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>225</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>250</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>275</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>325</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>350</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>375</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>plot_res!$E$2:$E$20</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>2.7959999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.5590000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.1919999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.0219999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.7809999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.7170000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.4449999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.409E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.243E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.038E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>8.6199999999999992E-3</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7.1599999999999997E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5.79E-3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>4.5500000000000002E-3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.1799999999999997E-3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3.3600000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>3.0799999999999998E-3</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2.7599999999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2.14E-3</c:v>
+                  <c:v>0.23777777777777778</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1446,6 +1156,7 @@
         <c:axId val="1921768159"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="50"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1456,27 +1167,45 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="1400">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
                   <a:t>Sample</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:rPr lang="en-US" sz="1400" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
                   <a:t> size</a:t>
                 </a:r>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-US" sz="1400">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1493,16 +1222,16 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1531,16 +1260,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1561,9 +1287,8 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1585,23 +1310,38 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Estimate</a:t>
+                  <a:rPr lang="en-US" sz="1400">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
+                  <a:t>Distance to optimum</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> a</a:t>
+                  <a:rPr lang="en-US" sz="1400" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                    <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  </a:rPr>
+                  <a:t> (STD units)</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>verage distance to the maximum</a:t>
-                </a:r>
+                <a:endParaRPr lang="en-US" sz="1400">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1625,9 +1365,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1656,16 +1396,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1677,73 +1414,14 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:legendEntry>
-        <c:idx val="4"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="5"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="6"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="7"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.80581174994635107"/>
-          <c:y val="0.11600623424877762"/>
-          <c:w val="0.16627214051073802"/>
-          <c:h val="0.27771153760574768"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="tx1"/>
           </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1760,12 +1438,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1783,8 +1456,9 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
+  <c:userShapes r:id="rId3"/>
 </c:chartSpace>
 </file>
 
@@ -2349,15 +2023,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
+      <xdr:colOff>232109</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>119061</xdr:rowOff>
+      <xdr:rowOff>8457</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
+      <xdr:colOff>194009</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>99391</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2383,6 +2057,527 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.62956</cdr:x>
+      <cdr:y>0.10522</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.94775</cdr:x>
+      <cdr:y>0.33115</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="13" name="Rectangle 12">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D7D68F0-9573-1DDF-14F6-E6737F539239}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="3834657" y="430521"/>
+          <a:ext cx="1938125" cy="924350"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525"/>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </cdr:style>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="en-US" kern="1200"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.65175</cdr:x>
+      <cdr:y>0.13648</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.71658</cdr:x>
+      <cdr:y>0.16671</cdr:y>
+    </cdr:to>
+    <cdr:grpSp>
+      <cdr:nvGrpSpPr>
+        <cdr:cNvPr id="22" name="Group 21">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11B5FB7A-8E8E-B76E-58FF-353E13160525}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvGrpSpPr/>
+      </cdr:nvGrpSpPr>
+      <cdr:grpSpPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="3969829" y="558399"/>
+          <a:ext cx="394881" cy="123684"/>
+          <a:chOff x="2296723" y="848055"/>
+          <a:chExt cx="259400" cy="87730"/>
+        </a:xfrm>
+      </cdr:grpSpPr>
+      <cdr:cxnSp macro="">
+        <cdr:nvCxnSpPr>
+          <cdr:cNvPr id="18" name="Straight Connector 17">
+            <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20EC9F73-E4C0-A95B-AEBB-15652DDD2677}"/>
+              </a:ext>
+            </a:extLst>
+          </cdr:cNvPr>
+          <cdr:cNvCxnSpPr/>
+        </cdr:nvCxnSpPr>
+        <cdr:spPr>
+          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:off x="2296723" y="890549"/>
+            <a:ext cx="259400" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:prstDash val="lgDash"/>
+          </a:ln>
+        </cdr:spPr>
+        <cdr:style>
+          <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </cdr:style>
+      </cdr:cxnSp>
+      <cdr:sp macro="" textlink="">
+        <cdr:nvSpPr>
+          <cdr:cNvPr id="14" name="Oval 13">
+            <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B352FB3A-31D2-17E1-A68E-A08B9F21A48E}"/>
+              </a:ext>
+            </a:extLst>
+          </cdr:cNvPr>
+          <cdr:cNvSpPr/>
+        </cdr:nvSpPr>
+        <cdr:spPr>
+          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:off x="2378600" y="848055"/>
+            <a:ext cx="84489" cy="87730"/>
+          </a:xfrm>
+          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+          </a:ln>
+        </cdr:spPr>
+        <cdr:style>
+          <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </cdr:style>
+        <cdr:txBody>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:endParaRPr lang="en-US" kern="1200"/>
+          </a:p>
+        </cdr:txBody>
+      </cdr:sp>
+    </cdr:grpSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.6516</cdr:x>
+      <cdr:y>0.21095</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.7193</cdr:x>
+      <cdr:y>0.23841</cdr:y>
+    </cdr:to>
+    <cdr:grpSp>
+      <cdr:nvGrpSpPr>
+        <cdr:cNvPr id="23" name="Group 22">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49666EC3-856B-992B-5E84-19174A306787}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvGrpSpPr/>
+      </cdr:nvGrpSpPr>
+      <cdr:grpSpPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="3968915" y="863088"/>
+          <a:ext cx="412363" cy="112351"/>
+          <a:chOff x="2299866" y="990888"/>
+          <a:chExt cx="259400" cy="65171"/>
+        </a:xfrm>
+      </cdr:grpSpPr>
+      <cdr:cxnSp macro="">
+        <cdr:nvCxnSpPr>
+          <cdr:cNvPr id="20" name="Straight Connector 19">
+            <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75DEF747-DFA9-98B8-1C6A-01AA473BB02B}"/>
+              </a:ext>
+            </a:extLst>
+          </cdr:cNvPr>
+          <cdr:cNvCxnSpPr/>
+        </cdr:nvCxnSpPr>
+        <cdr:spPr>
+          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:off x="2299866" y="1023988"/>
+            <a:ext cx="259400" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="sysDot"/>
+          </a:ln>
+        </cdr:spPr>
+        <cdr:style>
+          <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </cdr:style>
+      </cdr:cxnSp>
+      <cdr:sp macro="" textlink="">
+        <cdr:nvSpPr>
+          <cdr:cNvPr id="15" name="Rectangle 14">
+            <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32E995DD-ACFF-FFC8-2771-C1E7C26DFC89}"/>
+              </a:ext>
+            </a:extLst>
+          </cdr:cNvPr>
+          <cdr:cNvSpPr/>
+        </cdr:nvSpPr>
+        <cdr:spPr>
+          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:off x="2387867" y="990888"/>
+            <a:ext cx="64850" cy="65171"/>
+          </a:xfrm>
+          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </cdr:spPr>
+        <cdr:style>
+          <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </cdr:style>
+        <cdr:txBody>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:endParaRPr lang="en-US" kern="1200"/>
+          </a:p>
+        </cdr:txBody>
+      </cdr:sp>
+    </cdr:grpSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.65403</cdr:x>
+      <cdr:y>0.273</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.7125</cdr:x>
+      <cdr:y>0.30403</cdr:y>
+    </cdr:to>
+    <cdr:grpSp>
+      <cdr:nvGrpSpPr>
+        <cdr:cNvPr id="24" name="Group 23">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49751338-AA28-8EB0-7B85-F6F15EFBA368}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvGrpSpPr/>
+      </cdr:nvGrpSpPr>
+      <cdr:grpSpPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="3983716" y="1116961"/>
+          <a:ext cx="356143" cy="126958"/>
+          <a:chOff x="2297203" y="1129399"/>
+          <a:chExt cx="259400" cy="65773"/>
+        </a:xfrm>
+      </cdr:grpSpPr>
+      <cdr:cxnSp macro="">
+        <cdr:nvCxnSpPr>
+          <cdr:cNvPr id="21" name="Straight Connector 20">
+            <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71CE3FA1-A2FB-60F4-C258-5B71A3514A97}"/>
+              </a:ext>
+            </a:extLst>
+          </cdr:cNvPr>
+          <cdr:cNvCxnSpPr/>
+        </cdr:nvCxnSpPr>
+        <cdr:spPr>
+          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:off x="2297203" y="1166390"/>
+            <a:ext cx="259400" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="sysDash"/>
+          </a:ln>
+        </cdr:spPr>
+        <cdr:style>
+          <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </cdr:style>
+      </cdr:cxnSp>
+      <cdr:sp macro="" textlink="">
+        <cdr:nvSpPr>
+          <cdr:cNvPr id="16" name="Isosceles Triangle 15">
+            <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5753DFD1-1B6A-9777-3EB5-AF0465886259}"/>
+              </a:ext>
+            </a:extLst>
+          </cdr:cNvPr>
+          <cdr:cNvSpPr/>
+        </cdr:nvSpPr>
+        <cdr:spPr>
+          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:off x="2381988" y="1129399"/>
+            <a:ext cx="74826" cy="65773"/>
+          </a:xfrm>
+          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </cdr:spPr>
+        <cdr:style>
+          <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </cdr:style>
+        <cdr:txBody>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:endParaRPr lang="en-US" kern="1200"/>
+          </a:p>
+        </cdr:txBody>
+      </cdr:sp>
+    </cdr:grpSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.7193</cdr:x>
+      <cdr:y>0.08684</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.95999</cdr:x>
+      <cdr:y>0.34127</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="25" name="TextBox 24">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{325648C3-0A46-E9A6-C4DF-9FB2D0EF44AE}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="4381304" y="347696"/>
+          <a:ext cx="1466021" cy="1018761"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="l">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+              <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+            </a:rPr>
+            <a:t>Annealing</a:t>
+          </a:r>
+        </a:p>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="l">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+              <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+            </a:rPr>
+            <a:t>Random sketch</a:t>
+          </a:r>
+        </a:p>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="l">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="1200">
+              <a:latin typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+              <a:cs typeface="LMRoman12" panose="02000503020200000003" pitchFamily="50" charset="0"/>
+            </a:rPr>
+            <a:t>Quintuplets sketch</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2702,7 +2897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B210BE7F-76BC-43BC-AD62-F25D7661577D}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
@@ -2720,64 +2915,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>50</v>
-      </c>
-      <c r="B2">
-        <v>2.571E-2</v>
-      </c>
-      <c r="C2">
-        <v>3.2680000000000001E-2</v>
-      </c>
-      <c r="D2">
-        <v>2.6290000000000001E-2</v>
-      </c>
-      <c r="E2">
-        <v>2.7959999999999999E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>60</v>
-      </c>
-      <c r="B3">
-        <v>2.435E-2</v>
-      </c>
-      <c r="C3">
-        <v>3.1140000000000001E-2</v>
-      </c>
-      <c r="D3">
-        <v>2.3E-2</v>
-      </c>
-      <c r="E3">
-        <v>2.5590000000000002E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>70</v>
-      </c>
-      <c r="B4">
-        <v>2.3040000000000001E-2</v>
-      </c>
-      <c r="C4">
-        <v>2.9399999999999999E-2</v>
-      </c>
-      <c r="D4">
-        <v>2.052E-2</v>
-      </c>
-      <c r="E4">
-        <v>2.1919999999999999E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2790,9 +2931,6 @@
       <c r="C5">
         <v>2.878E-2</v>
       </c>
-      <c r="D5">
-        <v>1.9480000000000001E-2</v>
-      </c>
       <c r="E5">
         <v>2.0219999999999998E-2</v>
       </c>
@@ -2807,9 +2945,6 @@
       <c r="C6">
         <v>2.7730000000000001E-2</v>
       </c>
-      <c r="D6">
-        <v>1.7229999999999999E-2</v>
-      </c>
       <c r="E6">
         <v>1.7809999999999999E-2</v>
       </c>
@@ -2824,9 +2959,6 @@
       <c r="C7">
         <v>2.6679999999999999E-2</v>
       </c>
-      <c r="D7">
-        <v>1.738E-2</v>
-      </c>
       <c r="E7">
         <v>1.7170000000000001E-2</v>
       </c>
@@ -2841,9 +2973,6 @@
       <c r="C8">
         <v>2.538E-2</v>
       </c>
-      <c r="D8">
-        <v>1.6109999999999999E-2</v>
-      </c>
       <c r="E8">
         <v>1.4449999999999999E-2</v>
       </c>
@@ -2858,9 +2987,6 @@
       <c r="C9">
         <v>2.5020000000000001E-2</v>
       </c>
-      <c r="D9">
-        <v>1.4749999999999999E-2</v>
-      </c>
       <c r="E9">
         <v>1.409E-2</v>
       </c>
@@ -2875,9 +3001,6 @@
       <c r="C10">
         <v>2.426E-2</v>
       </c>
-      <c r="D10">
-        <v>1.3860000000000001E-2</v>
-      </c>
       <c r="E10">
         <v>1.243E-2</v>
       </c>
@@ -2892,9 +3015,6 @@
       <c r="C11">
         <v>2.3199999999999998E-2</v>
       </c>
-      <c r="D11">
-        <v>1.3310000000000001E-2</v>
-      </c>
       <c r="E11">
         <v>1.038E-2</v>
       </c>
@@ -2909,9 +3029,6 @@
       <c r="C12">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="D12">
-        <v>1.132E-2</v>
-      </c>
       <c r="E12">
         <v>8.6199999999999992E-3</v>
       </c>
@@ -2926,9 +3043,6 @@
       <c r="C13">
         <v>1.9879999999999998E-2</v>
       </c>
-      <c r="D13">
-        <v>9.92E-3</v>
-      </c>
       <c r="E13">
         <v>7.1599999999999997E-3</v>
       </c>
@@ -2943,9 +3057,6 @@
       <c r="C14">
         <v>1.907E-2</v>
       </c>
-      <c r="D14">
-        <v>8.9700000000000005E-3</v>
-      </c>
       <c r="E14">
         <v>5.79E-3</v>
       </c>
@@ -2960,9 +3071,6 @@
       <c r="C15">
         <v>1.8110000000000001E-2</v>
       </c>
-      <c r="D15">
-        <v>7.7400000000000004E-3</v>
-      </c>
       <c r="E15">
         <v>4.5500000000000002E-3</v>
       </c>
@@ -2977,9 +3085,6 @@
       <c r="C16">
         <v>1.7090000000000001E-2</v>
       </c>
-      <c r="D16">
-        <v>7.4400000000000004E-3</v>
-      </c>
       <c r="E16">
         <v>4.1799999999999997E-3</v>
       </c>
@@ -2994,9 +3099,6 @@
       <c r="C17">
         <v>1.6539999999999999E-2</v>
       </c>
-      <c r="D17">
-        <v>7.0600000000000003E-3</v>
-      </c>
       <c r="E17">
         <v>3.3600000000000001E-3</v>
       </c>
@@ -3011,9 +3113,6 @@
       <c r="C18">
         <v>1.542E-2</v>
       </c>
-      <c r="D18">
-        <v>6.43E-3</v>
-      </c>
       <c r="E18">
         <v>3.0799999999999998E-3</v>
       </c>
@@ -3028,9 +3127,6 @@
       <c r="C19">
         <v>1.461E-2</v>
       </c>
-      <c r="D19">
-        <v>6.2300000000000003E-3</v>
-      </c>
       <c r="E19">
         <v>2.7599999999999999E-3</v>
       </c>
@@ -3045,11 +3141,232 @@
       <c r="C20">
         <v>1.436E-2</v>
       </c>
-      <c r="D20">
-        <v>5.7000000000000002E-3</v>
-      </c>
       <c r="E20">
         <v>2.14E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f>B5/0.009</f>
+        <v>2.4622222222222225</v>
+      </c>
+      <c r="C23">
+        <f>C5/0.009</f>
+        <v>3.1977777777777781</v>
+      </c>
+      <c r="E23">
+        <f>E5/0.009</f>
+        <v>2.2466666666666666</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f t="shared" ref="B24:E24" si="0">B6/0.009</f>
+        <v>2.2811111111111111</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>3.0811111111111114</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>1.9788888888888889</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <f t="shared" ref="B25:E25" si="1">B7/0.009</f>
+        <v>2.1533333333333338</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="1"/>
+        <v>2.9644444444444447</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="1"/>
+        <v>1.907777777777778</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <f t="shared" ref="B26:E26" si="2">B8/0.009</f>
+        <v>1.9577777777777781</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="2"/>
+        <v>2.8200000000000003</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="2"/>
+        <v>1.6055555555555556</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <f t="shared" ref="B27:E27" si="3">B9/0.009</f>
+        <v>1.8255555555555558</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="3"/>
+        <v>2.7800000000000002</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="3"/>
+        <v>1.5655555555555556</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <f t="shared" ref="B28:E28" si="4">B10/0.009</f>
+        <v>1.6833333333333336</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="4"/>
+        <v>2.6955555555555559</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="4"/>
+        <v>1.3811111111111112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <f t="shared" ref="B29:E29" si="5">B11/0.009</f>
+        <v>1.5088888888888889</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="5"/>
+        <v>2.5777777777777779</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="5"/>
+        <v>1.1533333333333335</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <f t="shared" ref="B30:E30" si="6">B12/0.009</f>
+        <v>1.1233333333333333</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="6"/>
+        <v>2.2777777777777781</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="6"/>
+        <v>0.95777777777777773</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <f t="shared" ref="B31:E31" si="7">B13/0.009</f>
+        <v>0.94666666666666677</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="7"/>
+        <v>2.2088888888888887</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="7"/>
+        <v>0.79555555555555557</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <f t="shared" ref="B32:E32" si="8">B14/0.009</f>
+        <v>0.89444444444444449</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="8"/>
+        <v>2.1188888888888893</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="8"/>
+        <v>0.64333333333333342</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <f t="shared" ref="B33:E33" si="9">B15/0.009</f>
+        <v>0.7811111111111112</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="9"/>
+        <v>2.0122222222222224</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="9"/>
+        <v>0.50555555555555565</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <f t="shared" ref="B34:E34" si="10">B16/0.009</f>
+        <v>0.78666666666666674</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="10"/>
+        <v>1.8988888888888891</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="10"/>
+        <v>0.46444444444444444</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <f t="shared" ref="B35:E35" si="11">B17/0.009</f>
+        <v>0.74777777777777787</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="11"/>
+        <v>1.8377777777777777</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="11"/>
+        <v>0.37333333333333335</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <f t="shared" ref="B36:E36" si="12">B18/0.009</f>
+        <v>0.67333333333333345</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="12"/>
+        <v>1.7133333333333334</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="12"/>
+        <v>0.34222222222222221</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <f t="shared" ref="B37:E37" si="13">B19/0.009</f>
+        <v>0.68111111111111111</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="13"/>
+        <v>1.6233333333333335</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="13"/>
+        <v>0.3066666666666667</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <f t="shared" ref="B38:E38" si="14">B20/0.009</f>
+        <v>0.63444444444444448</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="14"/>
+        <v>1.5955555555555556</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="14"/>
+        <v>0.23777777777777778</v>
       </c>
     </row>
   </sheetData>
